--- a/data/CONSULTA_CIUDADANA.xlsx
+++ b/data/CONSULTA_CIUDADANA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-Distrito Cordoba\1-BASE DE DATOS\2-CONSULTA CIUDADANA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39223FB-C19C-483C-81A3-2EA8A0EFECC5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31056FB-31DB-492E-A0AB-C67929D0C0D8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8772" xr2:uid="{B8760439-6757-432A-9AD3-B20C010FCD58}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="296">
   <si>
     <t>Número de Cuenta</t>
   </si>
@@ -766,6 +766,162 @@
   </si>
   <si>
     <t>DPV</t>
+  </si>
+  <si>
+    <t>C_CIUD_079</t>
+  </si>
+  <si>
+    <t>C_CIUD_080</t>
+  </si>
+  <si>
+    <t>C_CIUD_081</t>
+  </si>
+  <si>
+    <t>MFR 1128244</t>
+  </si>
+  <si>
+    <t>BOSQUECILLO</t>
+  </si>
+  <si>
+    <t>Folio 27015  Año 1964</t>
+  </si>
+  <si>
+    <t>CARPETA 79</t>
+  </si>
+  <si>
+    <t>C_CIUD_082</t>
+  </si>
+  <si>
+    <t>C_CIUD_083</t>
+  </si>
+  <si>
+    <t>C_CIUD_084</t>
+  </si>
+  <si>
+    <t>C_CIUD_085</t>
+  </si>
+  <si>
+    <t>C_CIUD_086</t>
+  </si>
+  <si>
+    <t>C_CIUD_087</t>
+  </si>
+  <si>
+    <t>C_CIUD_088</t>
+  </si>
+  <si>
+    <t>C_CIUD_089</t>
+  </si>
+  <si>
+    <t>C_CIUD_090</t>
+  </si>
+  <si>
+    <t>C_CIUD_091</t>
+  </si>
+  <si>
+    <t>C_CIUD_092</t>
+  </si>
+  <si>
+    <t>C_CIUD_093</t>
+  </si>
+  <si>
+    <t>C_CIUD_094</t>
+  </si>
+  <si>
+    <t>C_CIUD_095</t>
+  </si>
+  <si>
+    <t>C_CIUD_096</t>
+  </si>
+  <si>
+    <t>C_CIUD_097</t>
+  </si>
+  <si>
+    <t>C_CIUD_098</t>
+  </si>
+  <si>
+    <t>C_CIUD_099</t>
+  </si>
+  <si>
+    <t>C_CIUD_100</t>
+  </si>
+  <si>
+    <t>CASA LAS PEÑAS</t>
+  </si>
+  <si>
+    <t>D 10431 F 12606 T 51 A 1942</t>
+  </si>
+  <si>
+    <t>CARPETA 11094</t>
+  </si>
+  <si>
+    <t>D  21860 F 24429 T  98  A  1948</t>
+  </si>
+  <si>
+    <t>CARPETA 60</t>
+  </si>
+  <si>
+    <t>RUTA NACIONAL Nº 9 KM, 621</t>
+  </si>
+  <si>
+    <t>CONSULTA CIUDADANA INTERCAMBIADOR</t>
+  </si>
+  <si>
+    <t>EX-2026-69180227-   -APN-DNV#MEC</t>
+  </si>
+  <si>
+    <t>OCUPACION CAMINERO DNV</t>
+  </si>
+  <si>
+    <t>PLANO 65545-1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTE ESPARCIMIENTO DNV </t>
+  </si>
+  <si>
+    <t>TRAMO ENTRE RIOS - MORENO</t>
+  </si>
+  <si>
+    <t>LOTE 30</t>
+  </si>
+  <si>
+    <t>CARPETA 5146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F° 39795 A°1953 </t>
+  </si>
+  <si>
+    <t> -64.335267</t>
+  </si>
+  <si>
+    <t>ACCESO B° Los Patagones - Rio Cuarto</t>
+  </si>
+  <si>
+    <t>DENUNCIA CIUDADANOS ACCESOS</t>
+  </si>
+  <si>
+    <t>CARPETA 3119</t>
+  </si>
+  <si>
+    <t>MFR 615143</t>
+  </si>
+  <si>
+    <t> -64.063843</t>
+  </si>
+  <si>
+    <t>CARPETA 26227</t>
+  </si>
+  <si>
+    <t>F 177 A 1947</t>
+  </si>
+  <si>
+    <t>LOTE 28</t>
+  </si>
+  <si>
+    <t>MFR 498006</t>
+  </si>
+  <si>
+    <t> -31.358483</t>
   </si>
 </sst>
 </file>
@@ -774,7 +930,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;GUI-&quot;000"/>
-    <numFmt numFmtId="169" formatCode="0.000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -877,7 +1033,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1194,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C52680-3297-46DC-AF10-C48147C1A639}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.5546875" style="1" customWidth="1"/>
@@ -3096,22 +3252,441 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
+      <c r="A86" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" s="9">
+        <v>-31.429276999999999</v>
+      </c>
+      <c r="C86" s="9">
+        <v>-63.138204000000002</v>
+      </c>
+      <c r="D86" s="3">
+        <v>3004523410486840</v>
+      </c>
+      <c r="E86" s="3">
+        <v>300403834908</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
+      <c r="A87" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B87" s="9">
+        <v>-34.036582000000003</v>
+      </c>
+      <c r="C87" s="9">
+        <v>-64.014634999999998</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2201004230499100</v>
+      </c>
+      <c r="E87" s="3">
+        <v>220119414377</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
+      <c r="A88" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B88" s="1">
+        <v>-34.136583999999999</v>
+      </c>
+      <c r="C88" s="1">
+        <v>-63.457369</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
+      <c r="A89" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B89" s="1">
+        <v>-30.556152000000001</v>
+      </c>
+      <c r="C89" s="1">
+        <v>-64.002646999999996</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
+      <c r="A90" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" s="1">
+        <v>-31.849377</v>
+      </c>
+      <c r="C90" s="1">
+        <v>-63.888899000000002</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
+      <c r="A91" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B91" s="1">
+        <v>-31.028358999999998</v>
+      </c>
+      <c r="C91" s="1">
+        <v>-64.505185999999995</v>
+      </c>
+      <c r="D91" s="3">
+        <v>2302531501205000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>230200990400</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B92" s="1">
+        <v>-34.804853000000001</v>
+      </c>
+      <c r="C92" s="1">
+        <v>-64.371556999999996</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B93" s="1">
+        <v>-31.654212000000001</v>
+      </c>
+      <c r="C93" s="1">
+        <v>-63.898963000000002</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B94" s="1">
+        <v>-31.352101999999999</v>
+      </c>
+      <c r="C94" s="1">
+        <v>-64.227367000000001</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B95" s="1">
+        <v>-33.918298</v>
+      </c>
+      <c r="C95" s="1">
+        <v>-64.406301999999997</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B96" s="1">
+        <v>-34.223083000000003</v>
+      </c>
+      <c r="C96" s="1">
+        <v>-64.395504000000003</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B97" s="1">
+        <v>-33.083545999999998</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B98" s="1">
+        <v>-31.433761000000001</v>
+      </c>
+      <c r="C98" s="1">
+        <v>-63.144306999999998</v>
+      </c>
+      <c r="D98" s="3">
+        <v>3004002210166900</v>
+      </c>
+      <c r="E98" s="3">
+        <v>300416918001</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B99" s="1">
+        <v>-31.460982000000001</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" s="3">
+        <v>1101012406001030</v>
+      </c>
+      <c r="E99" s="3">
+        <v>110117439801</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B100" s="1">
+        <v>-32.955328000000002</v>
+      </c>
+      <c r="C100" s="1">
+        <v>-64.356097000000005</v>
+      </c>
+      <c r="D100" s="3">
+        <v>2405353710373300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>240541064819</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" s="1">
+        <v>-31.420112</v>
+      </c>
+      <c r="C101" s="1">
+        <v>-62.062728</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B102" s="1">
+        <v>-33.092426000000003</v>
+      </c>
+      <c r="C102" s="1">
+        <v>-64.321775000000002</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B103" s="1">
+        <v>-30.841664999999999</v>
+      </c>
+      <c r="C103" s="1">
+        <v>-64.534163000000007</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B104" s="1">
+        <v>-32.368034999999999</v>
+      </c>
+      <c r="C104" s="1">
+        <v>-63.235630999999998</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B105" s="1">
+        <v>-33.197015999999998</v>
+      </c>
+      <c r="C105" s="1">
+        <v>-64.420034999999999</v>
+      </c>
+      <c r="D105" s="3">
+        <v>2405343660047600</v>
+      </c>
+      <c r="E105" s="3">
+        <v>240516672553</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B106" s="1">
+        <v>-33.221122999999999</v>
+      </c>
+      <c r="C106" s="1">
+        <v>-64.447046999999998</v>
+      </c>
+      <c r="D106" s="3">
+        <v>2405240101199100</v>
+      </c>
+      <c r="E106" s="3">
+        <v>240541964020</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C107" s="1">
+        <v>-64.203881999999993</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="4"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
